--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.70391602663816</v>
+        <v>5.314386354328701</v>
       </c>
       <c r="D2" t="n">
-        <v>32.87370913502866</v>
+        <v>5.341977734442158</v>
       </c>
       <c r="E2" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F2" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.7429373292066</v>
+        <v>9.383227315996072</v>
       </c>
       <c r="D3" t="n">
-        <v>58.09024426966729</v>
+        <v>9.439664693820935</v>
       </c>
       <c r="E3" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F3" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.38930346439958</v>
+        <v>5.100761812964931</v>
       </c>
       <c r="D4" t="n">
-        <v>11.98060579117169</v>
+        <v>1.9468484410654</v>
       </c>
       <c r="E4" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F4" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.1861510791578</v>
+        <v>8.480249550363142</v>
       </c>
       <c r="D5" t="n">
-        <v>51.7265965735339</v>
+        <v>8.405571943199259</v>
       </c>
       <c r="E5" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F5" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.5617919879147</v>
+        <v>9.19129119803614</v>
       </c>
       <c r="D6" t="n">
-        <v>56.23818958076641</v>
+        <v>9.138705806874542</v>
       </c>
       <c r="E6" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F6" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>87.47930780432274</v>
+        <v>14.21538751820245</v>
       </c>
       <c r="D7" t="n">
-        <v>87.02898349660597</v>
+        <v>14.14220981819847</v>
       </c>
       <c r="E7" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F7" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>98.99343969618668</v>
+        <v>16.08643395063034</v>
       </c>
       <c r="D8" t="n">
-        <v>67.59648596727095</v>
+        <v>10.98442896968153</v>
       </c>
       <c r="E8" t="n">
-        <v>23.65219181886842</v>
+        <v>3.843481170566119</v>
       </c>
       <c r="F8" t="n">
-        <v>22.33651247777036</v>
+        <v>3.629683277637684</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
